--- a/artfynd/A 22082-2026 artfynd.xlsx
+++ b/artfynd/A 22082-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,73 +675,62 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121253394</v>
+        <v>598176</v>
       </c>
       <c r="B2" t="n">
-        <v>56568</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>1560</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelört</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Thesium alpinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Trekanten, Grönskåra, Sm</t>
+          <t>1000 m VSV Flatehult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546867</v>
+        <v>546880</v>
       </c>
       <c r="R2" t="n">
-        <v>6323116</v>
+        <v>6323257</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +754,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2012-07-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2012-07-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Vägkorsning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,31 +775,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Grusvägsslänt</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Katharina Ahlert</t>
+          <t>Helena Lager</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Katharina Ahlert</t>
+          <t>Ekologa /Jonas Wäglind</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122281506</v>
+        <v>121253338</v>
       </c>
       <c r="B3" t="n">
-        <v>56594</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,16 +824,8 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>hane</t>
@@ -867,17 +843,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Traktorvägen, Grytsjön, Kråksmåla, Sm</t>
+          <t>Traktorvägen, Grönskåra, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546905</v>
+        <v>546885</v>
       </c>
       <c r="R3" t="n">
-        <v>6323155</v>
+        <v>6323232</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -901,22 +877,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -943,41 +919,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128427438</v>
+        <v>121253394</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>stationär</t>
@@ -990,14 +970,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+          <t>Trekanten, Grönskåra, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546859</v>
+        <v>546867</v>
       </c>
       <c r="R4" t="n">
-        <v>6323215</v>
+        <v>6323116</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1024,22 +1004,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1066,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128462920</v>
+        <v>122281506</v>
       </c>
       <c r="B5" t="n">
-        <v>58400</v>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1077,29 +1057,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1109,14 +1101,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+          <t>Traktorvägen, Grytsjön, Kråksmåla, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>546905</v>
       </c>
       <c r="R5" t="n">
-        <v>6323071</v>
+        <v>6323155</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1143,22 +1135,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1185,41 +1177,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128462775</v>
+        <v>129396247</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>stationär</t>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+          <t>Traktorvägen, Grytsjön, Kråksmåla, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546905</v>
+        <v>546799</v>
       </c>
       <c r="R6" t="n">
-        <v>6323071</v>
+        <v>6323237</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1266,22 +1266,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1308,44 +1308,44 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128462729</v>
+        <v>129416601</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1359,13 +1359,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546867</v>
+        <v>546857</v>
       </c>
       <c r="R7" t="n">
-        <v>6323145</v>
+        <v>6323131</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1389,22 +1389,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1431,10 +1431,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129416601</v>
+        <v>130109698</v>
       </c>
       <c r="B8" t="n">
-        <v>56926</v>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,14 +1461,22 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1482,13 +1490,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546857</v>
+        <v>546887</v>
       </c>
       <c r="R8" t="n">
-        <v>6323131</v>
+        <v>6323009</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1512,22 +1520,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1551,6 +1559,874 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130109743</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>546818</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6323187</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>15283639</v>
+      </c>
+      <c r="B10" t="n">
+        <v>45049</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Zygaena viciae</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>1000 m VSV Flatehult, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>546879</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6323257</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2012-07-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2012-07-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Grusvägsslänt</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Längs grusväg</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Helena Lager</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ekologa /Jonas Wäglind</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128427438</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>546859</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6323215</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128462729</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>546867</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6323145</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128462775</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>546905</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6323071</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128462864</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>546908</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6323249</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128462920</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>546905</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6323071</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22082-2026 artfynd.xlsx
+++ b/artfynd/A 22082-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/598176</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -916,6 +926,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121253338</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1043,6 +1058,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121253394</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1174,6 +1194,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122281506</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1305,6 +1330,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129396247</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1428,6 +1458,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129416601</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1559,6 +1594,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130109698</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1690,6 +1730,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130109743</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1816,6 +1861,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15283639</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1939,6 +1989,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128427438</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2062,6 +2117,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128462729</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2185,6 +2245,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128462775</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2308,6 +2373,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128462864</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2427,8 +2497,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128462920</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>